--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.03362178504597597</v>
       </c>
       <c r="C2" t="n">
-        <v>142893756</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>142893756</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>94661137</v>
+        <v>3599839</v>
       </c>
       <c r="L2" t="n">
-        <v>52230803</v>
+        <v>1729526</v>
       </c>
       <c r="M2" t="n">
-        <v>12712889</v>
+        <v>358806</v>
       </c>
       <c r="N2" t="n">
-        <v>654511</v>
+        <v>13015</v>
       </c>
       <c r="O2" t="n">
-        <v>7767197</v>
+        <v>230037</v>
       </c>
       <c r="P2" t="n">
-        <v>3222409</v>
+        <v>101382</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999021291732788</v>
+        <v>0.9998083114624023</v>
       </c>
       <c r="R2" t="n">
-        <v>0.839081346988678</v>
+        <v>0.7338399887084961</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6952549815177917</v>
+        <v>0.5293267965316772</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6037260293960571</v>
+        <v>0.392584353685379</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4189752638339996</v>
+        <v>0.1927291601896286</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6626559495925903</v>
+        <v>0.4515523016452789</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7272898554801941</v>
+        <v>0.5263234376907349</v>
       </c>
       <c r="X2" t="n">
-        <v>142893756</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>142893756</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>92470893</v>
+        <v>3557004</v>
       </c>
       <c r="AG2" t="n">
-        <v>48547434</v>
+        <v>1648362</v>
       </c>
       <c r="AH2" t="n">
-        <v>11617301</v>
+        <v>337891</v>
       </c>
       <c r="AI2" t="n">
-        <v>609421</v>
+        <v>12661</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7165306</v>
+        <v>216237</v>
       </c>
       <c r="AK2" t="n">
-        <v>3032452</v>
+        <v>95469</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8142338991165161</v>
+        <v>0.7203711271286011</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6587705016136169</v>
+        <v>0.5144560933113098</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5454007983207703</v>
+        <v>0.3648505210876465</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2998095154762268</v>
+        <v>0.1432596296072006</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6131927967071533</v>
+        <v>0.4256181418895721</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6822088956832886</v>
+        <v>0.4939848780632019</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.009468842884186441</v>
       </c>
       <c r="C3" t="n">
-        <v>4427</v>
+        <v>444</v>
       </c>
       <c r="D3" t="n">
-        <v>94661137</v>
+        <v>3599839</v>
       </c>
       <c r="E3" t="n">
-        <v>16323457</v>
+        <v>1105414</v>
       </c>
       <c r="F3" t="n">
-        <v>949239</v>
+        <v>88417</v>
       </c>
       <c r="G3" t="n">
-        <v>112270</v>
+        <v>8231</v>
       </c>
       <c r="H3" t="n">
-        <v>93574</v>
+        <v>11929</v>
       </c>
       <c r="I3" t="n">
-        <v>14955</v>
+        <v>2118</v>
       </c>
       <c r="J3" t="n">
-        <v>226711455</v>
+        <v>9856437</v>
       </c>
       <c r="K3" t="n">
-        <v>239306069</v>
+        <v>9948365</v>
       </c>
       <c r="L3" t="n">
-        <v>271868957</v>
+        <v>11228109</v>
       </c>
       <c r="M3" t="n">
-        <v>339794347</v>
+        <v>14573961</v>
       </c>
       <c r="N3" t="n">
-        <v>366665637</v>
+        <v>15926392</v>
       </c>
       <c r="O3" t="n">
-        <v>353932476</v>
+        <v>15278886</v>
       </c>
       <c r="P3" t="n">
-        <v>363959761</v>
+        <v>15785227</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8439900875091553</v>
+        <v>0.7474140524864197</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6977469325065613</v>
+        <v>0.5233993530273438</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5918377637863159</v>
+        <v>0.3811870217323303</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3199130296707153</v>
+        <v>0.1454303711652756</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6620178818702698</v>
+        <v>0.4491901099681854</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7239513993263245</v>
+        <v>0.522770881652832</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>92470893</v>
+        <v>3557004</v>
       </c>
       <c r="Z3" t="n">
-        <v>17897428</v>
+        <v>1114075</v>
       </c>
       <c r="AA3" t="n">
-        <v>1282774</v>
+        <v>106809</v>
       </c>
       <c r="AB3" t="n">
-        <v>361097</v>
+        <v>20519</v>
       </c>
       <c r="AC3" t="n">
-        <v>124681</v>
+        <v>14993</v>
       </c>
       <c r="AD3" t="n">
-        <v>22186</v>
+        <v>2992</v>
       </c>
       <c r="AE3" t="n">
-        <v>226725444</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>236363060</v>
+        <v>9873274</v>
       </c>
       <c r="AG3" t="n">
-        <v>269616262</v>
+        <v>11210265</v>
       </c>
       <c r="AH3" t="n">
-        <v>338455655</v>
+        <v>14540897</v>
       </c>
       <c r="AI3" t="n">
-        <v>366150024</v>
+        <v>15905190</v>
       </c>
       <c r="AJ3" t="n">
-        <v>353366655</v>
+        <v>15266468</v>
       </c>
       <c r="AK3" t="n">
-        <v>363755463</v>
+        <v>15778674</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8244621157646179</v>
+        <v>0.7385204434394836</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6485410928726196</v>
+        <v>0.4988369941711426</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.540833592414856</v>
+        <v>0.3589674234390259</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.297873854637146</v>
+        <v>0.1414747536182404</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6107171773910522</v>
+        <v>0.422243058681488</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6812753677368164</v>
+        <v>0.4922808110713959</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.07530134120129379</v>
       </c>
       <c r="C4" t="n">
-        <v>1703</v>
+        <v>163</v>
       </c>
       <c r="D4" t="n">
-        <v>16766974</v>
+        <v>1173545</v>
       </c>
       <c r="E4" t="n">
-        <v>52230803</v>
+        <v>1729526</v>
       </c>
       <c r="F4" t="n">
-        <v>4768804</v>
+        <v>302098</v>
       </c>
       <c r="G4" t="n">
-        <v>201533</v>
+        <v>15035</v>
       </c>
       <c r="H4" t="n">
-        <v>769918</v>
+        <v>71328</v>
       </c>
       <c r="I4" t="n">
-        <v>116636</v>
+        <v>12715</v>
       </c>
       <c r="J4" t="n">
-        <v>13989</v>
+        <v>1191</v>
       </c>
       <c r="K4" t="n">
-        <v>18154072</v>
+        <v>1305643</v>
       </c>
       <c r="L4" t="n">
-        <v>22893872</v>
+        <v>1537881</v>
       </c>
       <c r="M4" t="n">
-        <v>8344491</v>
+        <v>555153</v>
       </c>
       <c r="N4" t="n">
-        <v>907660</v>
+        <v>54515</v>
       </c>
       <c r="O4" t="n">
-        <v>3954115</v>
+        <v>279399</v>
       </c>
       <c r="P4" t="n">
-        <v>1208299</v>
+        <v>91241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999510645866394</v>
+        <v>0.9999041557312012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8415285348892212</v>
+        <v>0.74056476354599</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6964987516403198</v>
+        <v>0.5263463854789734</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5977227687835693</v>
+        <v>0.3868017196655273</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3628035485744476</v>
+        <v>0.1657718867063522</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6623367667198181</v>
+        <v>0.4503681063652039</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7256168127059937</v>
+        <v>0.5245411396026611</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>19361458</v>
+        <v>1226903</v>
       </c>
       <c r="Z4" t="n">
-        <v>48547434</v>
+        <v>1648362</v>
       </c>
       <c r="AA4" t="n">
-        <v>5494621</v>
+        <v>313588</v>
       </c>
       <c r="AB4" t="n">
-        <v>374306</v>
+        <v>22550</v>
       </c>
       <c r="AC4" t="n">
-        <v>929358</v>
+        <v>78235</v>
       </c>
       <c r="AD4" t="n">
-        <v>149194</v>
+        <v>14772</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>21097081</v>
+        <v>1380734</v>
       </c>
       <c r="AG4" t="n">
-        <v>25146567</v>
+        <v>1555725</v>
       </c>
       <c r="AH4" t="n">
-        <v>9683183</v>
+        <v>588217</v>
       </c>
       <c r="AI4" t="n">
-        <v>1423273</v>
+        <v>75717</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4519936</v>
+        <v>291817</v>
       </c>
       <c r="AK4" t="n">
-        <v>1412597</v>
+        <v>97794</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8193160891532898</v>
+        <v>0.7293328642845154</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6536158323287964</v>
+        <v>0.5065262317657471</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5431076288223267</v>
+        <v>0.3618850708007812</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2988385558128357</v>
+        <v>0.1423616111278534</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6119524836540222</v>
+        <v>0.4239239096641541</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.6817417740821838</v>
+        <v>0.4931313991546631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2659</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>988962</v>
+        <v>97802</v>
       </c>
       <c r="E5" t="n">
-        <v>5237484</v>
+        <v>318413</v>
       </c>
       <c r="F5" t="n">
-        <v>12712889</v>
+        <v>358806</v>
       </c>
       <c r="G5" t="n">
-        <v>324880</v>
+        <v>17113</v>
       </c>
       <c r="H5" t="n">
-        <v>1933075</v>
+        <v>124031</v>
       </c>
       <c r="I5" t="n">
-        <v>280413</v>
+        <v>24896</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>17497922</v>
+        <v>1216553</v>
       </c>
       <c r="L5" t="n">
-        <v>22625568</v>
+        <v>1574884</v>
       </c>
       <c r="M5" t="n">
-        <v>8767473</v>
+        <v>582480</v>
       </c>
       <c r="N5" t="n">
-        <v>1391392</v>
+        <v>76478</v>
       </c>
       <c r="O5" t="n">
-        <v>3965412</v>
+        <v>282078</v>
       </c>
       <c r="P5" t="n">
-        <v>1228731</v>
+        <v>92550</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999621510505676</v>
+        <v>0.9999259114265442</v>
       </c>
       <c r="R5" t="n">
-        <v>0.903544008731842</v>
+        <v>0.8430533409118652</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8768477439880371</v>
+        <v>0.8063044548034668</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9537038207054138</v>
+        <v>0.9292094111442566</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9937799572944641</v>
+        <v>0.9918488264083862</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9785737991333008</v>
+        <v>0.9650614261627197</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9934066534042358</v>
+        <v>0.9885633587837219</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1243172</v>
+        <v>113275</v>
       </c>
       <c r="Z5" t="n">
-        <v>5714002</v>
+        <v>318124</v>
       </c>
       <c r="AA5" t="n">
-        <v>11617301</v>
+        <v>337891</v>
       </c>
       <c r="AB5" t="n">
-        <v>385778</v>
+        <v>18281</v>
       </c>
       <c r="AC5" t="n">
-        <v>2182926</v>
+        <v>126497</v>
       </c>
       <c r="AD5" t="n">
-        <v>337183</v>
+        <v>27218</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>19688166</v>
+        <v>1259388</v>
       </c>
       <c r="AG5" t="n">
-        <v>26308937</v>
+        <v>1656048</v>
       </c>
       <c r="AH5" t="n">
-        <v>9863061</v>
+        <v>603395</v>
       </c>
       <c r="AI5" t="n">
-        <v>1436482</v>
+        <v>76832</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4567303</v>
+        <v>295878</v>
       </c>
       <c r="AK5" t="n">
-        <v>1418688</v>
+        <v>98463</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8896560668945312</v>
+        <v>0.8357152342796326</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8607878088951111</v>
+        <v>0.8001435399055481</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9471178650856018</v>
+        <v>0.925850510597229</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9922629594802856</v>
+        <v>0.9905074834823608</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9754145741462708</v>
+        <v>0.9634299874305725</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9923399686813354</v>
+        <v>0.987787663936615</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>3525</v>
+        <v>232</v>
       </c>
       <c r="D6" t="n">
-        <v>285595</v>
+        <v>18233</v>
       </c>
       <c r="E6" t="n">
-        <v>396084</v>
+        <v>24077</v>
       </c>
       <c r="F6" t="n">
-        <v>415494</v>
+        <v>17806</v>
       </c>
       <c r="G6" t="n">
-        <v>654511</v>
+        <v>13015</v>
       </c>
       <c r="H6" t="n">
-        <v>245784</v>
+        <v>12966</v>
       </c>
       <c r="I6" t="n">
-        <v>44910</v>
+        <v>3164</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>330691</v>
+        <v>19464</v>
       </c>
       <c r="Z6" t="n">
-        <v>395039</v>
+        <v>23674</v>
       </c>
       <c r="AA6" t="n">
-        <v>394356</v>
+        <v>17518</v>
       </c>
       <c r="AB6" t="n">
-        <v>609421</v>
+        <v>12661</v>
       </c>
       <c r="AC6" t="n">
-        <v>265398</v>
+        <v>12841</v>
       </c>
       <c r="AD6" t="n">
-        <v>50998</v>
+        <v>3335</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1095</v>
+        <v>98</v>
       </c>
       <c r="D7" t="n">
-        <v>105376</v>
+        <v>14816</v>
       </c>
       <c r="E7" t="n">
-        <v>847276</v>
+        <v>79749</v>
       </c>
       <c r="F7" t="n">
-        <v>2026675</v>
+        <v>127915</v>
       </c>
       <c r="G7" t="n">
-        <v>233605</v>
+        <v>11152</v>
       </c>
       <c r="H7" t="n">
-        <v>7767197</v>
+        <v>230037</v>
       </c>
       <c r="I7" t="n">
-        <v>751385</v>
+        <v>48348</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>149450</v>
+        <v>19084</v>
       </c>
       <c r="Z7" t="n">
-        <v>1025944</v>
+        <v>87959</v>
       </c>
       <c r="AA7" t="n">
-        <v>2280046</v>
+        <v>128273</v>
       </c>
       <c r="AB7" t="n">
-        <v>258827</v>
+        <v>11085</v>
       </c>
       <c r="AC7" t="n">
-        <v>7165306</v>
+        <v>216237</v>
       </c>
       <c r="AD7" t="n">
-        <v>853036</v>
+        <v>49477</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>580</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>7165</v>
+        <v>1247</v>
       </c>
       <c r="E8" t="n">
-        <v>89571</v>
+        <v>10228</v>
       </c>
       <c r="F8" t="n">
-        <v>184279</v>
+        <v>18917</v>
       </c>
       <c r="G8" t="n">
-        <v>35372</v>
+        <v>2984</v>
       </c>
       <c r="H8" t="n">
-        <v>911764</v>
+        <v>59145</v>
       </c>
       <c r="I8" t="n">
-        <v>3222409</v>
+        <v>101382</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>12310</v>
+        <v>2008</v>
       </c>
       <c r="Z8" t="n">
-        <v>114154</v>
+        <v>11893</v>
       </c>
       <c r="AA8" t="n">
-        <v>231386</v>
+        <v>22029</v>
       </c>
       <c r="AB8" t="n">
-        <v>43265</v>
+        <v>3282</v>
       </c>
       <c r="AC8" t="n">
-        <v>1017573</v>
+        <v>59251</v>
       </c>
       <c r="AD8" t="n">
-        <v>3032452</v>
+        <v>95469</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
